--- a/assets/constructions/examples/ctd_tgm_radial.xlsx
+++ b/assets/constructions/examples/ctd_tgm_radial.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AG6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,77 +574,103 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WGCM50L0432MC</t>
+          <t>VGAR-T10-3C</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WGC</t>
+          <t>VG-Cut</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WID_WC/G..04</t>
+          <t>VAR_VG_CUT-3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>VARGUS_VG_CUT_HPCR</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>VARGUS_VGD:3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="U2" t="n">
         <v>32</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>WC/G..04</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>WIDIA_50L</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>WIDIA_WGC:04</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>9.925000000000001</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
       <c r="V2" t="b">
         <v>0</v>
       </c>
@@ -652,10 +678,10 @@
         <v>2</v>
       </c>
       <c r="X2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
@@ -668,14 +694,28 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2017 / WIDIA Catalogue</t>
-        </is>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>317.35</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>29175.16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WGCM50L0212M</t>
+          <t>WMTWGMR2B16S</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -685,12 +725,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>WGC</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>WID_WC/G..02</t>
+          <t>WID_WMT..2B</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -699,22 +739,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>WC/G..02</t>
+          <t>WMT..2B</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>WIDIA_50L</t>
+          <t>WIDIA_GMR</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>WIDIA_WGC:02</t>
+          <t>WIDIA_WMT:2B</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -725,7 +765,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -735,11 +775,17 @@
         <v>0</v>
       </c>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.39</v>
+      </c>
       <c r="T3" t="n">
-        <v>10.875</v>
+        <v>10.71</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="b">
@@ -752,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
@@ -768,50 +814,52 @@
           <t>2017 / WIDIA Catalogue</t>
         </is>
       </c>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WMTWGML622S</t>
+          <t>VGAR20T25-3S</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>VG-Cut</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>WID_WMT..06</t>
+          <t>VAR_VG_CUT-3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>WIDIA</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>22</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>WMT..06</t>
-        </is>
-      </c>
+          <t>VARGUS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>40</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>WIDIA_GML</t>
+          <t>VARGUS_VG_CUTR20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>WIDIA_WMT:06</t>
+          <t>VARGUS_VGD:3</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -822,7 +870,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -831,20 +879,24 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>24</v>
+      </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>9.26</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>3.2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>20</v>
+      </c>
       <c r="V4" t="b">
         <v>0</v>
       </c>
@@ -868,49 +920,67 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2017 / WIDIA Catalogue</t>
-        </is>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>228.58</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>21014.21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VGAR-T30-5C</t>
+          <t>WGCM50L0516MC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VG-Cut</t>
+          <t>WGC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VAR_VG_CUT-5</t>
+          <t>WID_WC/G..05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>WC/G..05</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>VARGUS_VG_CUT_HPCR</t>
+          <t>WIDIA_50L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>VARGUS_VGD:5</t>
+          <t>WIDIA_WGC:05</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -921,33 +991,23 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>64</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>32</v>
-      </c>
+        <v>9.425000000000001</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="b">
         <v>0</v>
       </c>
@@ -955,10 +1015,10 @@
         <v>2</v>
       </c>
       <c r="X5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
@@ -971,49 +1031,59 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA Catalogue</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VGAL20T25-4S</t>
+          <t>WGCM65R0826MC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VG-Cut</t>
+          <t>WGC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VAR_VG_CUT-4</t>
+          <t>WID_WC/G..08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>44</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>WIDIA</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>26</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>WC/G..08</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>VARGUS_VG_CUTL20</t>
+          <t>WIDIA_65R</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>VARGUS_VGD:4</t>
+          <t>WIDIA_WGC:08</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -1024,33 +1094,23 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U6" t="n">
-        <v>20</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="b">
         <v>0</v>
       </c>
@@ -1058,10 +1118,10 @@
         <v>2</v>
       </c>
       <c r="X6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
@@ -1074,9 +1134,15 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA Catalogue</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
